--- a/data/daily/2026-09/2026-09-02.xlsx
+++ b/data/daily/2026-09/2026-09-02.xlsx
@@ -1245,14 +1245,64 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1317,60 +1367,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="342900" cy="457200"/>
+    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1500,27 +1500,77 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1528,104 +1578,54 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -2809,27 +2809,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>올인원 명품비타민 이뮨 멀티비타민 미네랄 7입+비타민젤리 마시는 액상 종합 비타민 수험생 직장인 부모님 건강 추석 선물</t>
+          <t>"한국인 맞춤 명품 비타민" 옵티젠 이뮨 멀티비타민&amp;미네랄 30입 / 1박스</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>옵티젠</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23,800원</t>
+          <t>59,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7948462</t>
+          <t>https://gift.kakao.com/product/11090567</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260902093524_a8f8c009362f4ec0affb7e118bf749cc.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260703113258_219f277f4a66466ea414f5539beed475.jpg</t>
         </is>
       </c>
     </row>
@@ -2844,27 +2844,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>"한국인 맞춤 명품 비타민" 옵티젠 이뮨 멀티비타민&amp;미네랄 30입 / 1박스</t>
+          <t>올인원 명품비타민 이뮨 멀티비타민 미네랄 7입+비타민젤리 마시는 액상 종합 비타민 수험생 직장인 부모님 건강 추석 선물</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>옵티젠</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>59,900원</t>
+          <t>23,800원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11090567</t>
+          <t>https://gift.kakao.com/product/7948462</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260703113258_219f277f4a66466ea414f5539beed475.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260902093524_a8f8c009362f4ec0affb7e118bf749cc.jpg</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
     <row r="13" ht="38" customHeight="1">
       <c r="B13" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2914,34 +2914,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로저당 단백칩 증정</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>46,900원</t>
+          <t>32,900원</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180343</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260831160758_47e2ca88a3ec4835979cf9737a40b276.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2949,34 +2949,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>65,900원</t>
+          <t>46,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965835</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260703103417_e8e422c5cf9740e3bfc2662a9aaa1eef.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2984,34 +2984,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
+          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>46,900원</t>
+          <t>65,900원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11566779</t>
+          <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260703103417_e8e422c5cf9740e3bfc2662a9aaa1eef.jpg</t>
         </is>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3019,27 +3019,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로저당 단백칩 증정</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>32,900원</t>
+          <t>46,900원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/13180343</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260831160758_47e2ca88a3ec4835979cf9737a40b276.jpg</t>
         </is>
       </c>
     </row>
@@ -3124,27 +3124,27 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>"이게 바로 찐! 초고함량" 액상스틱 L-아르기닌 7000 3박스 [케이스 동봉]</t>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>뉴트리디데이</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>30,900원</t>
+          <t>45,000원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4487367</t>
+          <t>https://gift.kakao.com/product/7417420</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260727151443_bd470867f85f4a79857e43d8b82ff835.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
         </is>
       </c>
     </row>
@@ -3159,27 +3159,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>"이게 바로 찐! 초고함량" 액상스틱 L-아르기닌 7000 3박스 [케이스 동봉]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>뉴트리디데이</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>45,000원</t>
+          <t>30,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7417420</t>
+          <t>https://gift.kakao.com/product/4487367</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260727151443_bd470867f85f4a79857e43d8b82ff835.jpg</t>
         </is>
       </c>
     </row>
@@ -3426,12 +3426,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
+          <t>옵티젠</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>종근당</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>옵티젠</t>
         </is>
       </c>
     </row>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
+          <t>"한국인 맞춤 명품 비타민" 옵티젠 이뮨 멀티비타민&amp;미네랄 30입 / 1박스</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>올인원 명품비타민 이뮨 멀티비타민 미네랄 7입+비타민젤리 마시는 액상 종합 비타민 수험생 직장인 부모님 건강 추석 선물</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>"한국인 맞춤 명품 비타민" 옵티젠 이뮨 멀티비타민&amp;미네랄 30입 / 1박스</t>
         </is>
       </c>
     </row>
@@ -3540,12 +3540,12 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
+          <t>59,900원</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
           <t>23,800원</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>59,900원</t>
         </is>
       </c>
     </row>
@@ -3693,22 +3693,22 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -3750,24 +3750,24 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>아일로</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>아일로</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
-        </is>
-      </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
           <t>셀렉스</t>
@@ -3780,12 +3780,12 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
           <t>뉴트리디데이</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>익스트림</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -3807,24 +3807,24 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)현미크리스피 닭가슴살 오리지널 1개</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
           <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로저당 단백칩 증정</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)현미크리스피 닭가슴살 오리지널 1개</t>
-        </is>
-      </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
           <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1+베리오트바 2EA</t>
@@ -3837,12 +3837,12 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
           <t>"이게 바로 찐! 초고함량" 액상스틱 L-아르기닌 7000 3박스 [케이스 동봉]</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -3864,24 +3864,24 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
+          <t>32,900원</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
           <t>46,900원</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>65,900원</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>46,900원</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>32,900원</t>
-        </is>
-      </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
           <t>27,900원</t>
@@ -3894,12 +3894,12 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>45,000원</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
           <t>30,900원</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>45,000원</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 10정 10일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4072,24 +4072,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000278&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/uooE7Z5tFnMjhhremBna600000278_00_01uooE7Z5tFnMjhhremBna.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 10정 10일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4107,24 +4107,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000281&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/H44oDYbaAQPekxvnTd9T600000281_00_01H44oDYbaAQPekxvnTd9T.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임Q10 6캡슐 6일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4142,24 +4142,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000279&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/OqWOmDxWU1qoZh2gUZfq600000279_00_01OqWOmDxWU1qoZh2gUZfq.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4167,34 +4167,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4202,34 +4202,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 멀티비타민 컴팩트 30정 30일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4252,19 +4252,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581101&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260601/nkEyZw9TcKRMHbTvSy6D591581101_00_00nkEyZw9TcKRMHbTvSy6D.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4272,34 +4272,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>오브맘 눈건강 루테인 하루구미 30일분</t>
+          <t>동화 바이마그랩 마그네슘 테아닌 5포 5일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602126&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618641&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251015/CucIwXdPFflEtkJEtXZl613602126_00_01CucIwXdPFflEtkJEtXZl.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/m3XnQVGNmWJfQCUZVnvy601618641_00_00m3XnQVGNmWJfQCUZVnvy.jpg</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4307,34 +4307,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>홀베리 유기농 레몬자몽즙 10포</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923433&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260305/0r6Ta1PlJSrc27DsREL6965923433_00_000r6Ta1PlJSrc27DsREL6.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
+          <t>대웅제약 비타민C 30정 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4357,19 +4357,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651649&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260325/RN6BLb2wWdxkL0nu9aVK600651649_00_00RN6BLb2wWdxkL0nu9aVK.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4377,27 +4377,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 밀크씨슬 12정 12일분</t>
+          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306204&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000203&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260406/RewRRgsZjRVv0Af38IFQ032306204_00_01RewRRgsZjRVv0Af38IFQ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251202/7FdyxsWTlcbRJnDROGoC600000203_00_007FdyxsWTlcbRJnDROGoC.jpg</t>
         </is>
       </c>
     </row>
@@ -4512,52 +4512,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>혈행</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -4584,37 +4584,37 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>대웅제약</t>
         </is>
       </c>
     </row>
@@ -4626,52 +4626,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 10정 10일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 10정 10일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임Q10 6캡슐 6일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 멀티비타민 컴팩트 30정 30일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 눈건강 루테인 하루구미 30일분</t>
+          <t>동화 바이마그랩 마그네슘 테아닌 5포 5일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>홀베리 유기농 레몬자몽즙 10포</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
+          <t>대웅제약 비타민C 30정 30일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 밀크씨슬 12정 12일분</t>
+          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
         </is>
       </c>
     </row>
@@ -4683,52 +4683,52 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>2,000원</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4945,34 +4945,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
+          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋 브이라인/글로우업 콜라겐 7포(+1포)/14포 (8/14일분)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>온리추얼</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17,770원</t>
+          <t>12,940원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247884&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236701&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024788480ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023670137ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4980,34 +4980,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24,460원</t>
+          <t>30,900원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733450ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5015,27 +5015,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>빌드 프리미엄 테프 효소 유산균 30포 (1개월분)</t>
+          <t>[스테디셀러 특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19,950원</t>
+          <t>14,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000235606&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023560605ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355476ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5050,27 +5050,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[스테디셀러 특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[1+1]알디콤 숙취해소제 4포입 3종 (플러스, 에이, 브이)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14,900원</t>
+          <t>13,320원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245840&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355476ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024584019ko.png?l=ko</t>
         </is>
       </c>
     </row>
@@ -5085,34 +5085,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 이너비 브이 캔디 14포 (+마이멜로디 마그넷액자)</t>
+          <t>[웰니스 특가]올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CJ이너비</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9,900원</t>
+          <t>8,800원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000264048&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026404809ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587417ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5120,34 +5120,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30,900원</t>
+          <t>34,010원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549618ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5155,34 +5155,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>34,010원</t>
+          <t>10,600원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000164736&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549618ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0016/A00000016473622ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5190,27 +5190,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
+          <t>[9월 올영픽/산리오콜라보] [반값특가] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>11,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225906&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022590605ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014343ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5335,42 +5335,42 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
         </is>
       </c>
     </row>
@@ -5392,42 +5392,42 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>온리추얼</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>CJ이너비</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
     </row>
@@ -5449,42 +5449,42 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
+          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋 브이라인/글로우업 콜라겐 7포(+1포)/14포 (8/14일분)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>빌드 프리미엄 테프 효소 유산균 30포 (1개월분)</t>
+          <t>[스테디셀러 특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>[스테디셀러 특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[1+1]알디콤 숙취해소제 4포입 3종 (플러스, 에이, 브이)</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 이너비 브이 캔디 14포 (+마이멜로디 마그넷액자)</t>
+          <t>[웰니스 특가]올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
+          <t>[9월 올영픽/산리오콜라보] [반값특가] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
     </row>
@@ -5506,42 +5506,42 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>17,770원</t>
+          <t>12,940원</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>24,460원</t>
+          <t>30,900원</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>19,950원</t>
+          <t>14,900원</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>14,900원</t>
+          <t>13,320원</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>9,900원</t>
+          <t>8,800원</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>30,900원</t>
+          <t>34,010원</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>34,010원</t>
+          <t>10,600원</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>11,900원</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -5677,10 +5677,10 @@
         <v>27.5</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
@@ -5689,23 +5689,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>22.5</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -5715,16 +5715,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -5733,36 +5733,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -5771,26 +5771,26 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -5799,23 +5799,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5843,7 +5843,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5853,10 +5853,10 @@
         <v>2.5</v>
       </c>
       <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
